--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -289,13 +289,13 @@
     <t>10034797</t>
   </si>
   <si>
-    <t>F/FLAG CHOCO TPK 110</t>
+    <t>FF CHOCO TPK 110 ML</t>
   </si>
   <si>
     <t>20096322</t>
   </si>
   <si>
-    <t>FF SS CAIR PLAIN 110</t>
+    <t>FF SS C PLAIN 110 ML</t>
   </si>
   <si>
     <t>20134172</t>
@@ -475,25 +475,25 @@
     <t>20077501</t>
   </si>
   <si>
-    <t>FF UHT COCONUT 946</t>
+    <t>FF UHT CNT.DL 946 ML</t>
   </si>
   <si>
     <t>20014069</t>
   </si>
   <si>
-    <t>FF UHT FULL CRM 946</t>
+    <t>FF UHT F CRM 946 ML</t>
   </si>
   <si>
     <t>20014071</t>
   </si>
   <si>
-    <t>FF UHT CHOCO 946ML</t>
+    <t>FF UHT CHOCO 946 ML</t>
   </si>
   <si>
     <t>20014070</t>
   </si>
   <si>
-    <t>F/F LOW FAT TPK 946</t>
+    <t>FF L.FAT TPK 946 ML</t>
   </si>
   <si>
     <t>20033547</t>
@@ -565,7 +565,7 @@
     <t>20129966</t>
   </si>
   <si>
-    <t>N/P MINUMAN LIME 330</t>
+    <t>N/P MNM LIME 330 ML</t>
   </si>
   <si>
     <t>20142239</t>
@@ -787,13 +787,13 @@
     <t>20048155</t>
   </si>
   <si>
-    <t>PUCUK/H TEH L/SGR350</t>
+    <t>PUCUK TH L.S 350 ML</t>
   </si>
   <si>
     <t>20035484</t>
   </si>
   <si>
-    <t>PUCUK/H TEH MLATI350</t>
+    <t>PUCUK TH MLTI 350 ML</t>
   </si>
   <si>
     <t>20072249</t>
@@ -1075,7 +1075,7 @@
     <t>20005530</t>
   </si>
   <si>
-    <t>NESTLE PURE LIFE 1.5</t>
+    <t>NESTLE MIN PL 1.5 ML</t>
   </si>
   <si>
     <t>20137992</t>
@@ -1186,7 +1186,7 @@
     <t>20005529</t>
   </si>
   <si>
-    <t>NESTLE PURE LIFE 600</t>
+    <t>NESTLE MIN PL 600 ML</t>
   </si>
   <si>
     <t>20037131</t>
@@ -1258,7 +1258,7 @@
     <t>20077499</t>
   </si>
   <si>
-    <t>PRISTINE 8.6+ BTL600</t>
+    <t>PRSTN 8 AIR B 600 ML</t>
   </si>
 </sst>
 </file>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -19,7 +19,7 @@
     <t>10000772</t>
   </si>
   <si>
-    <t>MARJAN MELON 460ML</t>
+    <t>MARJAN MELON 425ML</t>
   </si>
   <si>
     <t>BEV03S</t>
@@ -34,7 +34,7 @@
     <t>10000704</t>
   </si>
   <si>
-    <t>MARJAN COCOPDN 460ML</t>
+    <t>MARJAN COCOPANDAN425</t>
   </si>
   <si>
     <t>2</t>
@@ -43,7 +43,7 @@
     <t>10036619</t>
   </si>
   <si>
-    <t>MARJAN SRP LYCHE 460</t>
+    <t>MARJAN SRP LYCHE 425</t>
   </si>
   <si>
     <t>3</t>
@@ -55,7 +55,7 @@
     <t>20122092</t>
   </si>
   <si>
-    <t>MRJAN SYRP LEMON 460</t>
+    <t>MRJAN SYRP LEMON 425</t>
   </si>
   <si>
     <t>4</t>
@@ -64,7 +64,7 @@
     <t>10036617</t>
   </si>
   <si>
-    <t>MARJAN SYRP VNLA 460</t>
+    <t>MARJAN SYRP VNLA 425</t>
   </si>
   <si>
     <t>5</t>
@@ -73,7 +73,7 @@
     <t>10036611</t>
   </si>
   <si>
-    <t>MRJAN SYRP MOCCA 460</t>
+    <t>MRJAN SYRP MOCCA 425</t>
   </si>
   <si>
     <t>6</t>
@@ -391,7 +391,7 @@
     <t>20034079</t>
   </si>
   <si>
-    <t>F/FLAG COKLT TPK 225</t>
+    <t>F/FLAG CKT TP 225 ML</t>
   </si>
   <si>
     <t>10007380</t>
@@ -1114,7 +1114,7 @@
     <t>20085988</t>
   </si>
   <si>
-    <t>LE MINERALE 1500ML</t>
+    <t>LE MINERALE 1500 ML</t>
   </si>
   <si>
     <t>10004337</t>
@@ -1174,7 +1174,7 @@
     <t>20142495</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN 1L</t>
+    <t>IDM AIR MINE BTL 1 L</t>
   </si>
   <si>
     <t>10004336</t>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1152" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1146" uniqueCount="414">
   <si>
     <t/>
   </si>
@@ -190,19 +190,19 @@
     <t>10004779</t>
   </si>
   <si>
-    <t>INDOMILK KID CKL 115</t>
+    <t>INDOMLK KID CO 115 G</t>
   </si>
   <si>
     <t>10004780</t>
   </si>
   <si>
-    <t>INDOMILK KID STRW115</t>
+    <t>INDOMLK KID ST 115 G</t>
   </si>
   <si>
     <t>10004778</t>
   </si>
   <si>
-    <t>INDOMILK KID VNL 115</t>
+    <t>INDOMLK KID VA 115 G</t>
   </si>
   <si>
     <t>20088789</t>
@@ -397,19 +397,19 @@
     <t>10007380</t>
   </si>
   <si>
-    <t>ULTRA SLIM COKLAT200</t>
+    <t>ULTRA SLIM CO 200 ML</t>
   </si>
   <si>
     <t>10004401</t>
   </si>
   <si>
-    <t>INDOMILK UHT VAN 180</t>
+    <t>INDOMLK UHT VA 180 G</t>
   </si>
   <si>
     <t>20127735</t>
   </si>
   <si>
-    <t>INDMLK DLGNA COFF180</t>
+    <t>INDOMLK DL COF 180 G</t>
   </si>
   <si>
     <t>20080706</t>
@@ -601,7 +601,7 @@
     <t>20076052</t>
   </si>
   <si>
-    <t>PUCUK TEH MLTI 1.3L</t>
+    <t>PUCUK TH MLTI 1.3 L</t>
   </si>
   <si>
     <t>20096705</t>
@@ -1039,12 +1039,6 @@
     <t>HYDRO COCO 250ML</t>
   </si>
   <si>
-    <t>20115548</t>
-  </si>
-  <si>
-    <t>IDM COCONUT WTR 250</t>
-  </si>
-  <si>
     <t>20053540</t>
   </si>
   <si>
@@ -1105,7 +1099,7 @@
     <t>10000426</t>
   </si>
   <si>
-    <t>AQUA AIR MINERAL1500</t>
+    <t>AQUA AIR MINE 1.5 L</t>
   </si>
   <si>
     <t>17</t>
@@ -1144,7 +1138,7 @@
     <t>20090527</t>
   </si>
   <si>
-    <t>CRYSTALIN BTL 600mL</t>
+    <t>CRYSTLN AIR B 600 ML</t>
   </si>
   <si>
     <t>10003814</t>
@@ -1180,7 +1174,7 @@
     <t>10004336</t>
   </si>
   <si>
-    <t>INDOMARET AIR MIN600</t>
+    <t>IDM MINERAL 600 ML</t>
   </si>
   <si>
     <t>20005529</t>
@@ -1651,7 +1645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F192"/>
+  <dimension ref="A1:F191"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -4875,10 +4869,10 @@
         <v>100</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>107</v>
+        <v>34</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
@@ -4895,10 +4889,10 @@
         <v>100</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
@@ -4915,7 +4909,7 @@
         <v>100</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="F163" s="1" t="s">
         <v>12</v>
@@ -4932,30 +4926,30 @@
         <v>3</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
+        <v>351</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="C165" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D165" s="1" t="s">
         <v>350</v>
       </c>
-      <c r="B165" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="C165" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>352</v>
-      </c>
       <c r="E165" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F165" s="1" t="s">
         <v>34</v>
@@ -4972,10 +4966,10 @@
         <v>3</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F166" s="1" t="s">
         <v>34</v>
@@ -4992,10 +4986,10 @@
         <v>3</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E167" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F167" s="1" t="s">
         <v>34</v>
@@ -5012,10 +5006,10 @@
         <v>3</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E168" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F168" s="1" t="s">
         <v>34</v>
@@ -5032,13 +5026,13 @@
         <v>3</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E169" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
@@ -5052,33 +5046,33 @@
         <v>3</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>107</v>
+        <v>12</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C171" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D171" s="1" t="s">
         <v>363</v>
       </c>
-      <c r="B171" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="C171" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D171" s="1" t="s">
-        <v>365</v>
-      </c>
       <c r="E171" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
@@ -5092,33 +5086,33 @@
         <v>3</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E172" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>34</v>
+        <v>368</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B173" s="1" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C173" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D173" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="E173" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>370</v>
+        <v>110</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
@@ -5132,30 +5126,30 @@
         <v>3</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="E174" s="1" t="s">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>110</v>
+        <v>34</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C175" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D175" s="1" t="s">
         <v>373</v>
       </c>
-      <c r="B175" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="C175" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D175" s="1" t="s">
-        <v>375</v>
-      </c>
       <c r="E175" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F175" s="1" t="s">
         <v>34</v>
@@ -5172,33 +5166,33 @@
         <v>3</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E176" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="C177" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D177" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="B177" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="C177" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D177" s="1" t="s">
-        <v>380</v>
-      </c>
       <c r="E177" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
@@ -5212,10 +5206,10 @@
         <v>3</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="E178" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F178" s="1" t="s">
         <v>34</v>
@@ -5223,22 +5217,22 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="C179" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D179" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="B179" s="1" t="s">
-        <v>384</v>
-      </c>
-      <c r="C179" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>385</v>
-      </c>
       <c r="E179" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>34</v>
+        <v>107</v>
       </c>
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
@@ -5252,13 +5246,13 @@
         <v>3</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E180" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>107</v>
+        <v>368</v>
       </c>
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
@@ -5272,13 +5266,13 @@
         <v>3</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E181" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>370</v>
+        <v>34</v>
       </c>
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
@@ -5292,10 +5286,10 @@
         <v>3</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E182" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F182" s="1" t="s">
         <v>34</v>
@@ -5312,13 +5306,13 @@
         <v>3</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="E183" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>34</v>
+        <v>110</v>
       </c>
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
@@ -5332,30 +5326,30 @@
         <v>3</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="E184" s="1" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>110</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="C185" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D185" s="1" t="s">
         <v>396</v>
       </c>
-      <c r="B185" s="1" t="s">
-        <v>397</v>
-      </c>
-      <c r="C185" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D185" s="1" t="s">
-        <v>398</v>
-      </c>
       <c r="E185" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F185" s="1" t="s">
         <v>5</v>
@@ -5372,13 +5366,13 @@
         <v>3</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E186" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
@@ -5392,73 +5386,73 @@
         <v>3</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E187" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>12</v>
+        <v>403</v>
       </c>
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B188" s="1" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="C188" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E188" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B189" s="1" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C189" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E189" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="B190" s="1" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="C190" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E190" s="1" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>411</v>
+        <v>406</v>
       </c>
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
@@ -5472,32 +5466,12 @@
         <v>3</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="E191" s="1" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="192" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A192" s="1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B192" s="1" t="s">
-        <v>415</v>
-      </c>
-      <c r="C192" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D192" s="1" t="s">
-        <v>398</v>
-      </c>
-      <c r="E192" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F192" s="1" t="s">
         <v>110</v>
       </c>
     </row>

--- a/BEV03S.xlsx
+++ b/BEV03S.xlsx
@@ -130,19 +130,19 @@
     <t>20083795</t>
   </si>
   <si>
-    <t>F/FLAG UHT CHO 6X110</t>
+    <t>FF SS CHC B 6X110 ML</t>
   </si>
   <si>
     <t>20091183</t>
   </si>
   <si>
-    <t>F/FLAG UHT STR 6X110</t>
+    <t>FF SS STR B 6X110 ML</t>
   </si>
   <si>
     <t>20134673</t>
   </si>
   <si>
-    <t>F/FLAG UHT PLN 6X110</t>
+    <t>FF UHT PLN 6X110 ML</t>
   </si>
   <si>
     <t>20115354</t>
